--- a/data/output/sim_gridrnd/REL1/group_500_20/results/REL1_G4_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_500_20/results/REL1_G4_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,384 +466,439 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S02_G4_499_19_REL1</t>
+          <t>S01_G4_499_19_REL1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>499</v>
       </c>
       <c r="C2" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D2" t="n">
         <v>19</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E2" t="n">
         <v>499</v>
@@ -852,244 +907,277 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>492.00079395312</v>
-      </c>
-      <c r="J2" t="n">
-        <v>26.86796000851427</v>
-      </c>
-      <c r="K2" t="n">
-        <v>495.851514977968</v>
-      </c>
-      <c r="L2" t="n">
-        <v>26.52399248720085</v>
-      </c>
-      <c r="M2" t="n">
-        <v>498.5144523773337</v>
-      </c>
-      <c r="N2" t="n">
-        <v>28.34047436530516</v>
-      </c>
-      <c r="O2" t="n">
-        <v>500.2400353507754</v>
-      </c>
-      <c r="P2" t="n">
-        <v>26.08454736414402</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>502.0543534608655</v>
-      </c>
       <c r="R2" t="n">
-        <v>25.90616846849733</v>
+        <v>496.37</v>
       </c>
       <c r="S2" t="n">
-        <v>502.8319129077154</v>
+        <v>17.07</v>
       </c>
       <c r="T2" t="n">
-        <v>27.72938274932977</v>
+        <v>500.4</v>
       </c>
       <c r="U2" t="n">
-        <v>501.3959475050677</v>
+        <v>14.5</v>
       </c>
       <c r="V2" t="n">
-        <v>26.1229540100361</v>
+        <v>496.39</v>
       </c>
       <c r="W2" t="n">
-        <v>500.8876279227417</v>
+        <v>16.44</v>
       </c>
       <c r="X2" t="n">
-        <v>24.80815939854422</v>
+        <v>497.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>500.0782282392587</v>
+        <v>16.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>24.72131113899564</v>
+        <v>495.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>16.13</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>495.36</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>16.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>495.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>18.93</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>494.31</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>20.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>493.69</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>20.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>497.625</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>498.8333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>499.05</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>499.2</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>499.1416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>499.4785714285715</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>499.225</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>499.5222222222222</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>498.815</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>51.04835330351019</v>
+        <v>497.575</v>
       </c>
       <c r="AT2" t="n">
-        <v>44.29265050647668</v>
+        <v>498</v>
       </c>
       <c r="AU2" t="n">
-        <v>41.00240846584502</v>
+        <v>497.9625</v>
       </c>
       <c r="AV2" t="n">
-        <v>39.00794790808663</v>
+        <v>498.97</v>
       </c>
       <c r="AW2" t="n">
-        <v>36.37702934392649</v>
+        <v>498.9916666666667</v>
       </c>
       <c r="AX2" t="n">
-        <v>35.21474282519891</v>
+        <v>498.9642857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>34.03545026880062</v>
+        <v>498.7625</v>
       </c>
       <c r="AZ2" t="n">
-        <v>32.89418313244178</v>
+        <v>498.7388888888889</v>
       </c>
       <c r="BA2" t="n">
-        <v>32.00594905638638</v>
+        <v>498.655</v>
       </c>
       <c r="BB2" t="n">
-        <v>360</v>
+        <v>46.15944513314691</v>
       </c>
       <c r="BC2" t="n">
-        <v>360</v>
+        <v>40.07825678178465</v>
       </c>
       <c r="BD2" t="n">
-        <v>360</v>
+        <v>37.52613880683703</v>
       </c>
       <c r="BE2" t="n">
-        <v>360</v>
+        <v>34.63450735899097</v>
       </c>
       <c r="BF2" t="n">
-        <v>360</v>
+        <v>32.28325051615603</v>
       </c>
       <c r="BG2" t="n">
-        <v>360</v>
+        <v>30.82170170380551</v>
       </c>
       <c r="BH2" t="n">
-        <v>360</v>
+        <v>30.89791406794316</v>
       </c>
       <c r="BI2" t="n">
-        <v>360</v>
+        <v>31.29418900422407</v>
       </c>
       <c r="BJ2" t="n">
-        <v>360</v>
+        <v>31.36185541386223</v>
       </c>
       <c r="BK2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BL2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BM2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BN2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BO2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BP2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BQ2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BR2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BS2" t="n">
-        <v>669</v>
+        <v>332</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.75</v>
+        <v>589</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.6818181818181818</v>
+        <v>589</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.6666666666666666</v>
+        <v>589</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.7142857142857143</v>
+        <v>589</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.7619047619047619</v>
+        <v>589</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.8723404255319149</v>
+        <v>589</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.8518518518518519</v>
+        <v>589</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.8620689655172413</v>
+        <v>589</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.8620689655172413</v>
+        <v>589</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>0.868421052631579</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>0.8717948717948718</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>493.69</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>20.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S01_G4_499_19_REL1</t>
+          <t>S02_G4_499_19_REL1</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>499</v>
       </c>
       <c r="C3" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D3" t="n">
         <v>19</v>
-      </c>
-      <c r="D3" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E3" t="n">
         <v>499</v>
@@ -1098,228 +1186,261 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>496.3733585412189</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17.06575114888097</v>
-      </c>
-      <c r="K3" t="n">
-        <v>500.3992008096391</v>
-      </c>
-      <c r="L3" t="n">
-        <v>14.49795199097171</v>
-      </c>
-      <c r="M3" t="n">
-        <v>496.3878667672734</v>
-      </c>
-      <c r="N3" t="n">
-        <v>16.43757090316861</v>
-      </c>
-      <c r="O3" t="n">
-        <v>497.1034259952159</v>
-      </c>
-      <c r="P3" t="n">
-        <v>16.60246054869562</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>495.4462412345637</v>
-      </c>
       <c r="R3" t="n">
-        <v>16.13261964849324</v>
+        <v>492</v>
       </c>
       <c r="S3" t="n">
-        <v>495.3648977120771</v>
+        <v>26.87</v>
       </c>
       <c r="T3" t="n">
-        <v>16.89741188448432</v>
+        <v>495.85</v>
       </c>
       <c r="U3" t="n">
-        <v>495.3218602051145</v>
+        <v>26.52</v>
       </c>
       <c r="V3" t="n">
-        <v>18.93195587962493</v>
+        <v>498.51</v>
       </c>
       <c r="W3" t="n">
-        <v>494.3062305502015</v>
+        <v>28.34</v>
       </c>
       <c r="X3" t="n">
-        <v>20.30547672555267</v>
+        <v>500.24</v>
       </c>
       <c r="Y3" t="n">
-        <v>493.6910213752416</v>
+        <v>26.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.09863048175665</v>
+        <v>502.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>25.91</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>502.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>27.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>501.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>26.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>500.89</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>24.81</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>500.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>24.72</v>
       </c>
       <c r="AJ3" t="n">
-        <v>497.575</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>498</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>497.9625</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>498.97</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>498.9916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>498.9642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>498.7625</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>498.7388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>498.655</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>46.15944513314691</v>
+        <v>497.625</v>
       </c>
       <c r="AT3" t="n">
-        <v>40.07825678178465</v>
+        <v>498.8333333333333</v>
       </c>
       <c r="AU3" t="n">
-        <v>37.52613880683703</v>
+        <v>499.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>34.63450735899097</v>
+        <v>499.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>32.28325051615603</v>
+        <v>499.1416666666667</v>
       </c>
       <c r="AX3" t="n">
-        <v>30.82170170380551</v>
+        <v>499.4785714285715</v>
       </c>
       <c r="AY3" t="n">
-        <v>30.89791406794316</v>
+        <v>499.225</v>
       </c>
       <c r="AZ3" t="n">
-        <v>31.29418900422407</v>
+        <v>499.5222222222222</v>
       </c>
       <c r="BA3" t="n">
-        <v>31.36185541386223</v>
+        <v>498.815</v>
       </c>
       <c r="BB3" t="n">
-        <v>332</v>
+        <v>51.04835330351019</v>
       </c>
       <c r="BC3" t="n">
-        <v>332</v>
+        <v>44.29265050647668</v>
       </c>
       <c r="BD3" t="n">
-        <v>332</v>
+        <v>41.00240846584502</v>
       </c>
       <c r="BE3" t="n">
-        <v>332</v>
+        <v>39.00794790808663</v>
       </c>
       <c r="BF3" t="n">
-        <v>332</v>
+        <v>36.37702934392649</v>
       </c>
       <c r="BG3" t="n">
-        <v>332</v>
+        <v>35.21474282519891</v>
       </c>
       <c r="BH3" t="n">
-        <v>332</v>
+        <v>34.03545026880062</v>
       </c>
       <c r="BI3" t="n">
-        <v>332</v>
+        <v>32.89418313244178</v>
       </c>
       <c r="BJ3" t="n">
-        <v>332</v>
+        <v>32.00594905638638</v>
       </c>
       <c r="BK3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BL3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BM3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BN3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BO3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BP3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BQ3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BR3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BS3" t="n">
-        <v>589</v>
+        <v>360</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.8181818181818182</v>
+        <v>669</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.8</v>
+        <v>669</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.96</v>
+        <v>669</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.8928571428571429</v>
+        <v>669</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.9666666666666667</v>
+        <v>669</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.868421052631579</v>
+        <v>669</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.8717948717948718</v>
+        <v>669</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>500.08</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>24.72</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>498</v>
       </c>
       <c r="C4" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D4" t="n">
         <v>22</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E4" t="n">
         <v>498</v>
@@ -1344,720 +1465,819 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>488.0114153328498</v>
-      </c>
-      <c r="J4" t="n">
-        <v>21.97664133218217</v>
-      </c>
-      <c r="K4" t="n">
-        <v>490.3173055926145</v>
-      </c>
-      <c r="L4" t="n">
-        <v>19.39277135845136</v>
-      </c>
-      <c r="M4" t="n">
-        <v>494.1964485634685</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17.99544269722298</v>
-      </c>
-      <c r="O4" t="n">
-        <v>492.2625213025089</v>
-      </c>
-      <c r="P4" t="n">
-        <v>26.63958723053559</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>489.267789640166</v>
-      </c>
       <c r="R4" t="n">
-        <v>28.51322661521691</v>
+        <v>488.01</v>
       </c>
       <c r="S4" t="n">
-        <v>489.0995000280836</v>
+        <v>21.98</v>
       </c>
       <c r="T4" t="n">
-        <v>27.60261001377212</v>
+        <v>490.32</v>
       </c>
       <c r="U4" t="n">
-        <v>488.7244435824853</v>
+        <v>19.39</v>
       </c>
       <c r="V4" t="n">
-        <v>27.40124549795754</v>
+        <v>494.2</v>
       </c>
       <c r="W4" t="n">
-        <v>491.0970594685806</v>
+        <v>18</v>
       </c>
       <c r="X4" t="n">
-        <v>26.7543947214016</v>
+        <v>492.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>492.6864918347503</v>
+        <v>26.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>26.07499060815172</v>
+        <v>489.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>28.51</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>489.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>27.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>488.72</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>27.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>491.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>26.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>492.69</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>26.07</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>492.925</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>494.4833333333333</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>496.1875</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>496.95</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>497.8833333333333</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>498.3928571428572</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>497.83125</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>497.2555555555555</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>497.765</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>49.40566136587993</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>42.7338631012404</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>38.18379687445972</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>40.68817395755185</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>43.0587163714335</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>45.15523959924592</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>44.63563905039896</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>43.20585379863631</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>41.7100680291941</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>333</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>333</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>333</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>333</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>333</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>333</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>333</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>333</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>333</v>
       </c>
-      <c r="BK4" t="n">
+      <c r="BT4" t="n">
         <v>589</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BU4" t="n">
         <v>589</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BV4" t="n">
         <v>589</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BW4" t="n">
         <v>589</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BX4" t="n">
         <v>589</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BY4" t="n">
         <v>589</v>
       </c>
-      <c r="BQ4" t="n">
+      <c r="BZ4" t="n">
         <v>589</v>
       </c>
-      <c r="BR4" t="n">
+      <c r="CA4" t="n">
         <v>589</v>
       </c>
-      <c r="BS4" t="n">
+      <c r="CB4" t="n">
         <v>589</v>
       </c>
-      <c r="BT4" t="n">
+      <c r="CC4" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.5652173913043478</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.2173913043478261</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>1</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.92</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.9259259259259259</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>492.69</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>26.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G4_498_20_REL1</t>
+          <t>S04_G4_499_18_REL1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D5" t="n">
-        <v>29.65159377316531</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>493.5952095590621</v>
-      </c>
-      <c r="J5" t="n">
-        <v>19.47981288934935</v>
-      </c>
-      <c r="K5" t="n">
-        <v>490.9445683503194</v>
-      </c>
-      <c r="L5" t="n">
-        <v>21.42032199055836</v>
-      </c>
-      <c r="M5" t="n">
-        <v>492.5400536423212</v>
-      </c>
-      <c r="N5" t="n">
-        <v>19.6889579946458</v>
-      </c>
-      <c r="O5" t="n">
-        <v>490.6976727016927</v>
-      </c>
-      <c r="P5" t="n">
-        <v>18.98281338752164</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>490.3842495940416</v>
-      </c>
       <c r="R5" t="n">
-        <v>19.53015475459645</v>
+        <v>504.32</v>
       </c>
       <c r="S5" t="n">
-        <v>493.1317296053163</v>
+        <v>13.94</v>
       </c>
       <c r="T5" t="n">
-        <v>19.80165999117513</v>
+        <v>500.93</v>
       </c>
       <c r="U5" t="n">
-        <v>493.2122609130347</v>
+        <v>15.44</v>
       </c>
       <c r="V5" t="n">
-        <v>20.70638131834086</v>
+        <v>497.64</v>
       </c>
       <c r="W5" t="n">
-        <v>492.4907895711296</v>
+        <v>15.57</v>
       </c>
       <c r="X5" t="n">
-        <v>19.94125570172141</v>
+        <v>496.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>494.089229014257</v>
+        <v>17.47</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.64901598657963</v>
+        <v>496.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>17.23</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>499.69</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>19.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>499.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>21.92</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>497.33</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>22.67</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>496.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>22.86</v>
       </c>
       <c r="AJ5" t="n">
-        <v>498.825</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>498.4833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>499.0875</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>500.4</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>500.0416666666667</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>499.7928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>499.79375</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>500.1611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>500.52</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>50.42315316399799</v>
+        <v>505.15</v>
       </c>
       <c r="AT5" t="n">
-        <v>44.36646318510813</v>
+        <v>503.3833333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>40.14604393648271</v>
+        <v>502.65</v>
       </c>
       <c r="AV5" t="n">
-        <v>36.90203246435079</v>
+        <v>502</v>
       </c>
       <c r="AW5" t="n">
-        <v>34.89565298460859</v>
+        <v>501.7916666666667</v>
       </c>
       <c r="AX5" t="n">
-        <v>33.34141492167949</v>
+        <v>501.7928571428571</v>
       </c>
       <c r="AY5" t="n">
-        <v>32.49924939037054</v>
+        <v>500.925</v>
       </c>
       <c r="AZ5" t="n">
-        <v>31.22341783001429</v>
+        <v>500.8166666666667</v>
       </c>
       <c r="BA5" t="n">
-        <v>29.87908298458974</v>
+        <v>500.73</v>
       </c>
       <c r="BB5" t="n">
-        <v>360</v>
+        <v>50.10716016698611</v>
       </c>
       <c r="BC5" t="n">
-        <v>360</v>
+        <v>42.14897850350455</v>
       </c>
       <c r="BD5" t="n">
-        <v>360</v>
+        <v>37.67197234018947</v>
       </c>
       <c r="BE5" t="n">
-        <v>360</v>
+        <v>35.94217578277642</v>
       </c>
       <c r="BF5" t="n">
-        <v>360</v>
+        <v>33.7525050510658</v>
       </c>
       <c r="BG5" t="n">
-        <v>360</v>
+        <v>32.53009517103715</v>
       </c>
       <c r="BH5" t="n">
-        <v>360</v>
+        <v>32.40901687802332</v>
       </c>
       <c r="BI5" t="n">
-        <v>360</v>
+        <v>32.92710383053248</v>
       </c>
       <c r="BJ5" t="n">
-        <v>360</v>
+        <v>32.80910087155696</v>
       </c>
       <c r="BK5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BL5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BM5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BN5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BO5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BP5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BQ5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BR5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BS5" t="n">
-        <v>669</v>
+        <v>385</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.875</v>
+        <v>669</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.8666666666666667</v>
+        <v>669</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.9523809523809523</v>
+        <v>669</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.7096774193548387</v>
+        <v>669</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.7435897435897436</v>
+        <v>669</v>
       </c>
       <c r="BY5" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CJ5" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>0.7586206896551724</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>0.6714285714285714</v>
+      <c r="CK5" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>496.42</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>22.86</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S04_G4_499_18_REL1</t>
+          <t>S05_G4_498_20_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D6" t="n">
-        <v>26.68643439584878</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>504.3206346706466</v>
-      </c>
-      <c r="J6" t="n">
-        <v>13.94347749851092</v>
-      </c>
-      <c r="K6" t="n">
-        <v>500.932391672904</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15.44435372049301</v>
-      </c>
-      <c r="M6" t="n">
-        <v>497.6377050127992</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15.56746901131041</v>
-      </c>
-      <c r="O6" t="n">
-        <v>496.9653136612068</v>
-      </c>
-      <c r="P6" t="n">
-        <v>17.4720534773702</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>496.9439938577245</v>
-      </c>
       <c r="R6" t="n">
-        <v>17.22687568535275</v>
+        <v>493.6</v>
       </c>
       <c r="S6" t="n">
-        <v>499.6878931445034</v>
+        <v>19.48</v>
       </c>
       <c r="T6" t="n">
-        <v>19.34115615824481</v>
+        <v>490.94</v>
       </c>
       <c r="U6" t="n">
-        <v>499.0767186372444</v>
+        <v>21.42</v>
       </c>
       <c r="V6" t="n">
-        <v>21.91899503386527</v>
+        <v>492.54</v>
       </c>
       <c r="W6" t="n">
-        <v>497.3322799379929</v>
+        <v>19.69</v>
       </c>
       <c r="X6" t="n">
-        <v>22.66986454432418</v>
+        <v>490.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>496.4229055974491</v>
+        <v>18.98</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.86339781626064</v>
+        <v>490.38</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>19.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>493.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>493.21</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>20.71</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>492.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>19.94</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>494.09</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>19.65</v>
       </c>
       <c r="AJ6" t="n">
-        <v>505.15</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>503.3833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>502.65</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>501.7916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>501.7928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>500.925</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>500.8166666666667</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>500.73</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>50.10716016698611</v>
+        <v>498.825</v>
       </c>
       <c r="AT6" t="n">
-        <v>42.14897850350455</v>
+        <v>498.4833333333333</v>
       </c>
       <c r="AU6" t="n">
-        <v>37.67197234018947</v>
+        <v>499.0875</v>
       </c>
       <c r="AV6" t="n">
-        <v>35.94217578277642</v>
+        <v>500.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>33.7525050510658</v>
+        <v>500.0416666666667</v>
       </c>
       <c r="AX6" t="n">
-        <v>32.53009517103715</v>
+        <v>499.7928571428571</v>
       </c>
       <c r="AY6" t="n">
-        <v>32.40901687802332</v>
+        <v>499.79375</v>
       </c>
       <c r="AZ6" t="n">
-        <v>32.92710383053248</v>
+        <v>500.1611111111111</v>
       </c>
       <c r="BA6" t="n">
-        <v>32.80910087155696</v>
+        <v>500.52</v>
       </c>
       <c r="BB6" t="n">
-        <v>385</v>
+        <v>50.42315316399799</v>
       </c>
       <c r="BC6" t="n">
-        <v>385</v>
+        <v>44.36646318510813</v>
       </c>
       <c r="BD6" t="n">
-        <v>385</v>
+        <v>40.14604393648271</v>
       </c>
       <c r="BE6" t="n">
-        <v>385</v>
+        <v>36.90203246435079</v>
       </c>
       <c r="BF6" t="n">
-        <v>385</v>
+        <v>34.89565298460859</v>
       </c>
       <c r="BG6" t="n">
-        <v>385</v>
+        <v>33.34141492167949</v>
       </c>
       <c r="BH6" t="n">
-        <v>385</v>
+        <v>32.49924939037054</v>
       </c>
       <c r="BI6" t="n">
-        <v>385</v>
+        <v>31.22341783001429</v>
       </c>
       <c r="BJ6" t="n">
-        <v>385</v>
+        <v>29.87908298458974</v>
       </c>
       <c r="BK6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BL6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BM6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BN6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BO6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BP6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BQ6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BR6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BS6" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.5</v>
+        <v>669</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.5333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.5588235294117647</v>
+        <v>669</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.6341463414634146</v>
+        <v>669</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.6041666666666666</v>
+        <v>669</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.6875</v>
+        <v>669</v>
       </c>
       <c r="CA6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.7096774193548387</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="CH6" t="n">
         <v>0.75</v>
       </c>
-      <c r="CB6" t="n">
-        <v>0.8541666666666666</v>
+      <c r="CI6" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.6714285714285714</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>494.09</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>19.65</v>
       </c>
     </row>
     <row r="7">
@@ -2070,10 +2290,10 @@
         <v>502</v>
       </c>
       <c r="C7" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D7" t="n">
         <v>18</v>
-      </c>
-      <c r="D7" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E7" t="n">
         <v>502</v>
@@ -2082,228 +2302,261 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>517.4225133541446</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.454923617150462</v>
-      </c>
-      <c r="K7" t="n">
-        <v>507.026427721063</v>
-      </c>
-      <c r="L7" t="n">
-        <v>12.09375404069583</v>
-      </c>
-      <c r="M7" t="n">
-        <v>500.2889741267246</v>
-      </c>
-      <c r="N7" t="n">
-        <v>14.27190657502092</v>
-      </c>
-      <c r="O7" t="n">
-        <v>499.3026388556027</v>
-      </c>
-      <c r="P7" t="n">
-        <v>15.82733511452065</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>499.0848140090036</v>
-      </c>
       <c r="R7" t="n">
-        <v>14.71172290688384</v>
+        <v>517.42</v>
       </c>
       <c r="S7" t="n">
-        <v>498.5560081829045</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>14.54257981847369</v>
+        <v>507.03</v>
       </c>
       <c r="U7" t="n">
-        <v>499.0888152324323</v>
+        <v>12.09</v>
       </c>
       <c r="V7" t="n">
-        <v>16.55813003294482</v>
+        <v>500.29</v>
       </c>
       <c r="W7" t="n">
-        <v>498.9742627316381</v>
+        <v>14.27</v>
       </c>
       <c r="X7" t="n">
-        <v>18.21391690929099</v>
+        <v>499.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>499.8797560087453</v>
+        <v>15.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.83165413587125</v>
+        <v>499.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>14.71</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>498.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>14.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>499.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>16.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>498.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>18.21</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>499.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>19.83</v>
       </c>
       <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>503.6</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AT7" t="n">
         <v>502.65</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AU7" t="n">
         <v>502.9375</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AV7" t="n">
         <v>502.2</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AW7" t="n">
         <v>501.925</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AX7" t="n">
         <v>501.4428571428571</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AY7" t="n">
         <v>501.1</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AZ7" t="n">
         <v>500.8166666666667</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="BA7" t="n">
         <v>500.74</v>
       </c>
-      <c r="AS7" t="n">
+      <c r="BB7" t="n">
         <v>48.53442077536313</v>
       </c>
-      <c r="AT7" t="n">
+      <c r="BC7" t="n">
         <v>40.91365908837781</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
         <v>36.44493920628761</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="BE7" t="n">
         <v>33.34516456699532</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="BF7" t="n">
         <v>31.11300973869291</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="BG7" t="n">
         <v>29.22383357774253</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
         <v>28.13254343282882</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BI7" t="n">
         <v>28.26373314180402</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BJ7" t="n">
         <v>28.71589107097323</v>
       </c>
-      <c r="BB7" t="n">
+      <c r="BK7" t="n">
         <v>373</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
         <v>373</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BM7" t="n">
         <v>373</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BN7" t="n">
         <v>373</v>
       </c>
-      <c r="BF7" t="n">
+      <c r="BO7" t="n">
         <v>373</v>
       </c>
-      <c r="BG7" t="n">
+      <c r="BP7" t="n">
         <v>373</v>
       </c>
-      <c r="BH7" t="n">
+      <c r="BQ7" t="n">
         <v>373</v>
       </c>
-      <c r="BI7" t="n">
+      <c r="BR7" t="n">
         <v>373</v>
       </c>
-      <c r="BJ7" t="n">
+      <c r="BS7" t="n">
         <v>373</v>
       </c>
-      <c r="BK7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>669</v>
-      </c>
       <c r="BT7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC7" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BU7" t="n">
+      <c r="CD7" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="BV7" t="n">
+      <c r="CE7" t="n">
         <v>0.6206896551724138</v>
       </c>
-      <c r="BW7" t="n">
+      <c r="CF7" t="n">
         <v>0.5897435897435898</v>
       </c>
-      <c r="BX7" t="n">
+      <c r="CG7" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BY7" t="n">
+      <c r="CH7" t="n">
         <v>0.576271186440678</v>
       </c>
-      <c r="BZ7" t="n">
+      <c r="CI7" t="n">
         <v>0.5507246376811594</v>
       </c>
-      <c r="CA7" t="n">
+      <c r="CJ7" t="n">
         <v>0.5797101449275363</v>
       </c>
-      <c r="CB7" t="n">
+      <c r="CK7" t="n">
         <v>0.5942028985507246</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>499.88</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>19.83</v>
       </c>
     </row>
     <row r="8">
@@ -2316,10 +2569,10 @@
         <v>498</v>
       </c>
       <c r="C8" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D8" t="n">
         <v>20</v>
-      </c>
-      <c r="D8" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E8" t="n">
         <v>498</v>
@@ -2328,228 +2581,261 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>502.9059912128538</v>
-      </c>
-      <c r="J8" t="n">
-        <v>15.90872271120712</v>
-      </c>
-      <c r="K8" t="n">
-        <v>503.1724803841497</v>
-      </c>
-      <c r="L8" t="n">
-        <v>14.36751867605622</v>
-      </c>
-      <c r="M8" t="n">
-        <v>502.1608892524022</v>
-      </c>
-      <c r="N8" t="n">
-        <v>19.35221863814865</v>
-      </c>
-      <c r="O8" t="n">
-        <v>502.9177972644165</v>
-      </c>
-      <c r="P8" t="n">
-        <v>22.07412090922953</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>499.2396692764118</v>
-      </c>
       <c r="R8" t="n">
-        <v>21.95205792857254</v>
+        <v>502.91</v>
       </c>
       <c r="S8" t="n">
-        <v>497.3535564746817</v>
+        <v>15.91</v>
       </c>
       <c r="T8" t="n">
-        <v>23.15025721483538</v>
+        <v>503.17</v>
       </c>
       <c r="U8" t="n">
-        <v>494.4648449353582</v>
+        <v>14.37</v>
       </c>
       <c r="V8" t="n">
-        <v>22.41343770952422</v>
+        <v>502.16</v>
       </c>
       <c r="W8" t="n">
-        <v>494.2977819061479</v>
+        <v>19.35</v>
       </c>
       <c r="X8" t="n">
-        <v>22.73072482917038</v>
+        <v>502.92</v>
       </c>
       <c r="Y8" t="n">
-        <v>495.9557672249419</v>
+        <v>22.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.86717775240858</v>
+        <v>499.24</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>21.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>497.35</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>494.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>22.41</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>494.3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>22.73</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>495.96</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>21.87</v>
       </c>
       <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>498.075</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AT8" t="n">
         <v>498.1</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AU8" t="n">
         <v>497.75</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AV8" t="n">
         <v>497.57</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AW8" t="n">
         <v>497.775</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AX8" t="n">
         <v>498.5857142857143</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AY8" t="n">
         <v>498.93125</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AZ8" t="n">
         <v>498.8444444444444</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="BA8" t="n">
         <v>499.19</v>
       </c>
-      <c r="AS8" t="n">
+      <c r="BB8" t="n">
         <v>47.74378886305526</v>
       </c>
-      <c r="AT8" t="n">
+      <c r="BC8" t="n">
         <v>40.67583230043773</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="BD8" t="n">
         <v>39.35495521532199</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BE8" t="n">
         <v>40.4581895294389</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="BF8" t="n">
         <v>38.51784489038814</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="BG8" t="n">
         <v>36.71861842138822</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BH8" t="n">
         <v>35.56633272404536</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BI8" t="n">
         <v>34.62125587012538</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BJ8" t="n">
         <v>33.60065326745895</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BK8" t="n">
         <v>325</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BL8" t="n">
         <v>325</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BM8" t="n">
         <v>325</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BN8" t="n">
         <v>325</v>
       </c>
-      <c r="BF8" t="n">
+      <c r="BO8" t="n">
         <v>325</v>
       </c>
-      <c r="BG8" t="n">
+      <c r="BP8" t="n">
         <v>325</v>
       </c>
-      <c r="BH8" t="n">
+      <c r="BQ8" t="n">
         <v>325</v>
       </c>
-      <c r="BI8" t="n">
+      <c r="BR8" t="n">
         <v>325</v>
       </c>
-      <c r="BJ8" t="n">
+      <c r="BS8" t="n">
         <v>325</v>
       </c>
-      <c r="BK8" t="n">
+      <c r="BT8" t="n">
         <v>610</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BU8" t="n">
         <v>610</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BV8" t="n">
         <v>610</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BW8" t="n">
         <v>610</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BX8" t="n">
         <v>610</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BY8" t="n">
         <v>610</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BZ8" t="n">
         <v>610</v>
       </c>
-      <c r="BR8" t="n">
+      <c r="CA8" t="n">
         <v>610</v>
       </c>
-      <c r="BS8" t="n">
+      <c r="CB8" t="n">
         <v>610</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="CC8" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="CD8" t="n">
         <v>0.5</v>
       </c>
-      <c r="BV8" t="n">
+      <c r="CE8" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BW8" t="n">
+      <c r="CF8" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="CG8" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="CH8" t="n">
         <v>0.75</v>
       </c>
-      <c r="BZ8" t="n">
+      <c r="CI8" t="n">
         <v>0.7222222222222222</v>
       </c>
-      <c r="CA8" t="n">
+      <c r="CJ8" t="n">
         <v>0.7380952380952381</v>
       </c>
-      <c r="CB8" t="n">
+      <c r="CK8" t="n">
         <v>0.7083333333333334</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>495.96</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>21.87</v>
       </c>
     </row>
     <row r="9">
@@ -2562,10 +2848,10 @@
         <v>500</v>
       </c>
       <c r="C9" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D9" t="n">
         <v>19</v>
-      </c>
-      <c r="D9" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E9" t="n">
         <v>500</v>
@@ -2574,228 +2860,261 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>515.4849438332393</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.363808426245297</v>
-      </c>
-      <c r="K9" t="n">
-        <v>511.9990556717466</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10.06701197933249</v>
-      </c>
-      <c r="M9" t="n">
-        <v>508.0945763609473</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15.44452400456096</v>
-      </c>
-      <c r="O9" t="n">
-        <v>504.6993441555301</v>
-      </c>
-      <c r="P9" t="n">
-        <v>21.459980509016</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>506.7474532698095</v>
-      </c>
       <c r="R9" t="n">
-        <v>20.63602872082404</v>
+        <v>515.48</v>
       </c>
       <c r="S9" t="n">
-        <v>504.6659020706813</v>
+        <v>4.36</v>
       </c>
       <c r="T9" t="n">
-        <v>20.10572046736557</v>
+        <v>512</v>
       </c>
       <c r="U9" t="n">
-        <v>503.4330789625832</v>
+        <v>10.07</v>
       </c>
       <c r="V9" t="n">
-        <v>20.69329134090307</v>
+        <v>508.09</v>
       </c>
       <c r="W9" t="n">
-        <v>502.9302452345229</v>
+        <v>15.44</v>
       </c>
       <c r="X9" t="n">
-        <v>20.71054700410885</v>
+        <v>504.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>501.7283514830506</v>
+        <v>21.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.02804079525465</v>
+        <v>506.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>20.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>504.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>20.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>503.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>20.69</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>502.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>20.71</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>501.73</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>21.03</v>
       </c>
       <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
         <v>498.675</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AT9" t="n">
         <v>498.45</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AU9" t="n">
         <v>498.5625</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AV9" t="n">
         <v>498.97</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AW9" t="n">
         <v>499.2666666666667</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AX9" t="n">
         <v>499.5571428571429</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AY9" t="n">
         <v>499.61875</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
         <v>499.2222222222222</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="BA9" t="n">
         <v>499.37</v>
       </c>
-      <c r="AS9" t="n">
+      <c r="BB9" t="n">
         <v>50.17787734649603</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BC9" t="n">
         <v>42.76151891595995</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BD9" t="n">
         <v>38.47299174420934</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="BE9" t="n">
         <v>35.71315023909261</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="BF9" t="n">
         <v>34.46102468328854</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="BG9" t="n">
         <v>33.65906191472947</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BH9" t="n">
         <v>32.3664316605569</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BI9" t="n">
         <v>30.85729799425369</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BJ9" t="n">
         <v>29.92211723792286</v>
       </c>
-      <c r="BB9" t="n">
+      <c r="BK9" t="n">
         <v>326</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BL9" t="n">
         <v>326</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BM9" t="n">
         <v>326</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BN9" t="n">
         <v>326</v>
       </c>
-      <c r="BF9" t="n">
+      <c r="BO9" t="n">
         <v>326</v>
       </c>
-      <c r="BG9" t="n">
+      <c r="BP9" t="n">
         <v>326</v>
       </c>
-      <c r="BH9" t="n">
+      <c r="BQ9" t="n">
         <v>326</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BR9" t="n">
         <v>326</v>
       </c>
-      <c r="BJ9" t="n">
+      <c r="BS9" t="n">
         <v>326</v>
       </c>
-      <c r="BK9" t="n">
+      <c r="BT9" t="n">
         <v>639</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BU9" t="n">
         <v>639</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BV9" t="n">
         <v>639</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BW9" t="n">
         <v>639</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BX9" t="n">
         <v>639</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BY9" t="n">
         <v>639</v>
       </c>
-      <c r="BQ9" t="n">
+      <c r="BZ9" t="n">
         <v>639</v>
       </c>
-      <c r="BR9" t="n">
+      <c r="CA9" t="n">
         <v>639</v>
       </c>
-      <c r="BS9" t="n">
+      <c r="CB9" t="n">
         <v>639</v>
       </c>
-      <c r="BT9" t="n">
+      <c r="CC9" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="CD9" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BV9" t="n">
+      <c r="CE9" t="n">
         <v>0.6060606060606061</v>
       </c>
-      <c r="BW9" t="n">
+      <c r="CF9" t="n">
         <v>0.6511627906976745</v>
       </c>
-      <c r="BX9" t="n">
+      <c r="CG9" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BY9" t="n">
+      <c r="CH9" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BZ9" t="n">
+      <c r="CI9" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="CA9" t="n">
+      <c r="CJ9" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="CB9" t="n">
+      <c r="CK9" t="n">
         <v>0.7936507936507936</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>501.73</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>21.03</v>
       </c>
     </row>
     <row r="10">
@@ -2808,10 +3127,10 @@
         <v>499</v>
       </c>
       <c r="C10" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D10" t="n">
         <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E10" t="n">
         <v>499</v>
@@ -2820,228 +3139,261 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>494.1740996162116</v>
-      </c>
-      <c r="J10" t="n">
-        <v>19.62992862941729</v>
-      </c>
-      <c r="K10" t="n">
-        <v>499.2490896474169</v>
-      </c>
-      <c r="L10" t="n">
-        <v>28.10981051831109</v>
-      </c>
-      <c r="M10" t="n">
-        <v>501.4503690293517</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25.23344862975993</v>
-      </c>
-      <c r="O10" t="n">
-        <v>497.6129476685842</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22.1154182635529</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>497.0108697922889</v>
-      </c>
       <c r="R10" t="n">
-        <v>20.8125572223314</v>
+        <v>494.17</v>
       </c>
       <c r="S10" t="n">
-        <v>496.2042323908539</v>
+        <v>19.63</v>
       </c>
       <c r="T10" t="n">
-        <v>20.34334999627059</v>
+        <v>499.25</v>
       </c>
       <c r="U10" t="n">
-        <v>497.1991558309131</v>
+        <v>28.11</v>
       </c>
       <c r="V10" t="n">
-        <v>20.76806528938454</v>
+        <v>501.45</v>
       </c>
       <c r="W10" t="n">
-        <v>498.2543087173404</v>
+        <v>25.23</v>
       </c>
       <c r="X10" t="n">
-        <v>19.79202666824992</v>
+        <v>497.61</v>
       </c>
       <c r="Y10" t="n">
-        <v>500.001620994079</v>
+        <v>22.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.13543932460051</v>
+        <v>497.01</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>20.81</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>496.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>20.34</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>497.2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>20.77</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>498.25</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>19.79</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>20.14</v>
       </c>
       <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
         <v>501.85</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AT10" t="n">
         <v>502.4</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AU10" t="n">
         <v>501.9125</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AV10" t="n">
         <v>500.92</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AW10" t="n">
         <v>500.5833333333333</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AX10" t="n">
         <v>500.7214285714286</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AY10" t="n">
         <v>500.44375</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AZ10" t="n">
         <v>500.4277777777778</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="BA10" t="n">
         <v>500.765</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BB10" t="n">
         <v>49.15106814709117</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="BC10" t="n">
         <v>44.96302184388115</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BD10" t="n">
         <v>44.73985743998298</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="BE10" t="n">
         <v>41.67413586386645</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="BF10" t="n">
         <v>38.89528320446524</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="BG10" t="n">
         <v>37.18776063191123</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BH10" t="n">
         <v>35.50206805155863</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BI10" t="n">
         <v>34.2443881137326</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BJ10" t="n">
         <v>32.96452297546561</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BK10" t="n">
         <v>339</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BL10" t="n">
         <v>339</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BM10" t="n">
         <v>339</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BN10" t="n">
         <v>339</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BO10" t="n">
         <v>339</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BP10" t="n">
         <v>339</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BQ10" t="n">
         <v>339</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BR10" t="n">
         <v>339</v>
       </c>
-      <c r="BJ10" t="n">
+      <c r="BS10" t="n">
         <v>339</v>
       </c>
-      <c r="BK10" t="n">
+      <c r="BT10" t="n">
         <v>636</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BU10" t="n">
         <v>636</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BV10" t="n">
         <v>636</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BW10" t="n">
         <v>636</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BX10" t="n">
         <v>636</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BY10" t="n">
         <v>636</v>
       </c>
-      <c r="BQ10" t="n">
+      <c r="BZ10" t="n">
         <v>636</v>
       </c>
-      <c r="BR10" t="n">
+      <c r="CA10" t="n">
         <v>636</v>
       </c>
-      <c r="BS10" t="n">
+      <c r="CB10" t="n">
         <v>636</v>
       </c>
-      <c r="BT10" t="n">
+      <c r="CC10" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU10" t="n">
+      <c r="CD10" t="n">
         <v>0.9230769230769231</v>
       </c>
-      <c r="BV10" t="n">
+      <c r="CE10" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW10" t="n">
+      <c r="CF10" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BX10" t="n">
+      <c r="CG10" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BY10" t="n">
+      <c r="CH10" t="n">
         <v>0.8846153846153846</v>
       </c>
-      <c r="BZ10" t="n">
+      <c r="CI10" t="n">
         <v>0.9375</v>
       </c>
-      <c r="CA10" t="n">
+      <c r="CJ10" t="n">
         <v>0.9722222222222222</v>
       </c>
-      <c r="CB10" t="n">
+      <c r="CK10" t="n">
         <v>1</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>20.14</v>
       </c>
     </row>
     <row r="11">
@@ -3054,10 +3406,10 @@
         <v>499</v>
       </c>
       <c r="C11" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D11" t="n">
         <v>22</v>
-      </c>
-      <c r="D11" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E11" t="n">
         <v>499</v>
@@ -3066,228 +3418,261 @@
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>487.7155770353131</v>
-      </c>
-      <c r="J11" t="n">
-        <v>39.82513037061648</v>
-      </c>
-      <c r="K11" t="n">
-        <v>489.491799435429</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30.29959073561412</v>
-      </c>
-      <c r="M11" t="n">
-        <v>492.1991549381953</v>
-      </c>
-      <c r="N11" t="n">
-        <v>29.86402794031786</v>
-      </c>
-      <c r="O11" t="n">
-        <v>492.9937644661366</v>
-      </c>
-      <c r="P11" t="n">
-        <v>29.2472549944493</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>496.1326058964979</v>
-      </c>
       <c r="R11" t="n">
-        <v>28.00670671148321</v>
+        <v>487.72</v>
       </c>
       <c r="S11" t="n">
-        <v>493.6994599134111</v>
+        <v>39.83</v>
       </c>
       <c r="T11" t="n">
-        <v>27.07330523960611</v>
+        <v>489.49</v>
       </c>
       <c r="U11" t="n">
-        <v>493.4043102359943</v>
+        <v>30.3</v>
       </c>
       <c r="V11" t="n">
-        <v>25.48110159461211</v>
+        <v>492.2</v>
       </c>
       <c r="W11" t="n">
-        <v>494.5685474643167</v>
+        <v>29.86</v>
       </c>
       <c r="X11" t="n">
-        <v>26.95912797797441</v>
+        <v>492.99</v>
       </c>
       <c r="Y11" t="n">
-        <v>494.3804031985997</v>
+        <v>29.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>25.0906782370595</v>
+        <v>496.13</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>28.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>493.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>27.07</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>493.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>25.48</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>494.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>26.96</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>494.38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>25.09</v>
       </c>
       <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
         <v>497.35</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AT11" t="n">
         <v>498.2</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AU11" t="n">
         <v>498.0625</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AV11" t="n">
         <v>498.5</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AW11" t="n">
         <v>497.95</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AX11" t="n">
         <v>497.9142857142857</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AY11" t="n">
         <v>497.53125</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AZ11" t="n">
         <v>498.1444444444444</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="BA11" t="n">
         <v>498.01</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="BB11" t="n">
         <v>61.13900146387738</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="BC11" t="n">
         <v>54.23553570615241</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="BD11" t="n">
         <v>50.03882086690292</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="BE11" t="n">
         <v>45.82957560353358</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="BF11" t="n">
         <v>43.12053841655196</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="BG11" t="n">
         <v>40.35494052145035</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BH11" t="n">
         <v>39.18528452668808</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BI11" t="n">
         <v>37.59877690419408</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BJ11" t="n">
         <v>36.68800757740873</v>
       </c>
-      <c r="BB11" t="n">
+      <c r="BK11" t="n">
         <v>322</v>
       </c>
-      <c r="BC11" t="n">
+      <c r="BL11" t="n">
         <v>322</v>
       </c>
-      <c r="BD11" t="n">
+      <c r="BM11" t="n">
         <v>322</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BN11" t="n">
         <v>322</v>
       </c>
-      <c r="BF11" t="n">
+      <c r="BO11" t="n">
         <v>322</v>
       </c>
-      <c r="BG11" t="n">
+      <c r="BP11" t="n">
         <v>322</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BQ11" t="n">
         <v>322</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BR11" t="n">
         <v>322</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BS11" t="n">
         <v>322</v>
       </c>
-      <c r="BK11" t="n">
+      <c r="BT11" t="n">
         <v>639</v>
       </c>
-      <c r="BL11" t="n">
+      <c r="BU11" t="n">
         <v>639</v>
       </c>
-      <c r="BM11" t="n">
+      <c r="BV11" t="n">
         <v>639</v>
       </c>
-      <c r="BN11" t="n">
+      <c r="BW11" t="n">
         <v>639</v>
       </c>
-      <c r="BO11" t="n">
+      <c r="BX11" t="n">
         <v>639</v>
       </c>
-      <c r="BP11" t="n">
+      <c r="BY11" t="n">
         <v>639</v>
       </c>
-      <c r="BQ11" t="n">
+      <c r="BZ11" t="n">
         <v>639</v>
       </c>
-      <c r="BR11" t="n">
+      <c r="CA11" t="n">
         <v>639</v>
       </c>
-      <c r="BS11" t="n">
+      <c r="CB11" t="n">
         <v>639</v>
       </c>
-      <c r="BT11" t="n">
+      <c r="CC11" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BU11" t="n">
+      <c r="CD11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BV11" t="n">
+      <c r="CE11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BW11" t="n">
+      <c r="CF11" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BX11" t="n">
+      <c r="CG11" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="BY11" t="n">
+      <c r="CH11" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ11" t="n">
+      <c r="CI11" t="n">
         <v>0.9</v>
       </c>
-      <c r="CA11" t="n">
+      <c r="CJ11" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="CB11" t="n">
+      <c r="CK11" t="n">
         <v>0.9411764705882353</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>494.38</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>25.09</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>498</v>
       </c>
       <c r="C12" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D12" t="n">
         <v>19</v>
-      </c>
-      <c r="D12" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E12" t="n">
         <v>498</v>
@@ -3312,228 +3697,261 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>490.8081214439401</v>
-      </c>
-      <c r="J12" t="n">
-        <v>23.34509303342352</v>
-      </c>
-      <c r="K12" t="n">
-        <v>494.6977039289098</v>
-      </c>
-      <c r="L12" t="n">
-        <v>23.82590251037399</v>
-      </c>
-      <c r="M12" t="n">
-        <v>496.7502621335782</v>
-      </c>
-      <c r="N12" t="n">
-        <v>21.76480532785551</v>
-      </c>
-      <c r="O12" t="n">
-        <v>499.699281468072</v>
-      </c>
-      <c r="P12" t="n">
-        <v>21.15057471325609</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>503.4601081154766</v>
-      </c>
       <c r="R12" t="n">
-        <v>19.85158550707439</v>
+        <v>490.81</v>
       </c>
       <c r="S12" t="n">
-        <v>500.3134228484338</v>
+        <v>23.35</v>
       </c>
       <c r="T12" t="n">
-        <v>19.52072670312973</v>
+        <v>494.7</v>
       </c>
       <c r="U12" t="n">
-        <v>500.3126730483564</v>
+        <v>23.83</v>
       </c>
       <c r="V12" t="n">
-        <v>21.25864173461116</v>
+        <v>496.75</v>
       </c>
       <c r="W12" t="n">
-        <v>501.188529698614</v>
+        <v>21.76</v>
       </c>
       <c r="X12" t="n">
-        <v>21.13350440145735</v>
+        <v>499.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>502.1459461479215</v>
+        <v>21.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.80060319386928</v>
+        <v>503.46</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>19.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>500.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>19.52</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>500.31</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>21.26</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>501.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>21.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>502.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>500.15</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>499.9</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>500.0375</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>499.61</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>499.0416666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>498.8</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>499.0125</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>498.7055555555556</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>498.83</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>54.75881207623117</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>47.27568085178679</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>42.61350834829256</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>38.89187447269673</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>36.02878382472671</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>34.05671739906828</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>32.62207601839589</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>33.03831062775157</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>32.27895754202729</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>352</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>352</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>352</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>352</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>352</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>352</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>352</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>352</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>352</v>
       </c>
-      <c r="BK12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>669</v>
-      </c>
       <c r="BT12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC12" t="n">
         <v>0.6153846153846154</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="CG12" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="CH12" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.7692307692307693</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.7674418604651163</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.8222222222222222</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>502.15</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>20.8</v>
       </c>
     </row>
     <row r="13">
@@ -3546,10 +3964,10 @@
         <v>502</v>
       </c>
       <c r="C13" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D13" t="n">
         <v>22</v>
-      </c>
-      <c r="D13" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E13" t="n">
         <v>502</v>
@@ -3558,228 +3976,261 @@
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>75.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>503.4130512265927</v>
-      </c>
-      <c r="J13" t="n">
-        <v>19.32394549636074</v>
-      </c>
-      <c r="K13" t="n">
-        <v>500.0779247555909</v>
-      </c>
-      <c r="L13" t="n">
-        <v>16.50151730748917</v>
-      </c>
-      <c r="M13" t="n">
-        <v>500.7705677378476</v>
-      </c>
-      <c r="N13" t="n">
-        <v>15.84200071990314</v>
-      </c>
-      <c r="O13" t="n">
-        <v>497.6972751093647</v>
-      </c>
-      <c r="P13" t="n">
-        <v>18.11333686781166</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>499.4012016376581</v>
-      </c>
       <c r="R13" t="n">
-        <v>18.88083978863764</v>
+        <v>503.41</v>
       </c>
       <c r="S13" t="n">
-        <v>497.4310792830049</v>
+        <v>19.32</v>
       </c>
       <c r="T13" t="n">
-        <v>18.32397374582563</v>
+        <v>500.08</v>
       </c>
       <c r="U13" t="n">
-        <v>497.1695450134353</v>
+        <v>16.5</v>
       </c>
       <c r="V13" t="n">
-        <v>18.58505491048167</v>
+        <v>500.77</v>
       </c>
       <c r="W13" t="n">
-        <v>496.741779665439</v>
+        <v>15.84</v>
       </c>
       <c r="X13" t="n">
-        <v>18.73744325161193</v>
+        <v>497.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>498.3566451429865</v>
+        <v>18.11</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.37460851025228</v>
+        <v>499.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>497.43</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>18.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>497.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>18.59</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>496.74</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>18.74</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>498.36</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
         <v>500.65</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AT13" t="n">
         <v>501</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AU13" t="n">
         <v>501.275</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AV13" t="n">
         <v>501</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AW13" t="n">
         <v>500.4</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AX13" t="n">
         <v>500.3071428571429</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AY13" t="n">
         <v>500.33125</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="AZ13" t="n">
         <v>500.4222222222222</v>
       </c>
-      <c r="AR13" t="n">
+      <c r="BA13" t="n">
         <v>500.315</v>
       </c>
-      <c r="AS13" t="n">
+      <c r="BB13" t="n">
         <v>47.6804729422853</v>
       </c>
-      <c r="AT13" t="n">
+      <c r="BC13" t="n">
         <v>41.32795663954365</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="BD13" t="n">
         <v>37.51532186987071</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="BE13" t="n">
         <v>36.96079003484638</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="BF13" t="n">
         <v>36.27795473838071</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="BG13" t="n">
         <v>33.91647227877237</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BH13" t="n">
         <v>32.94801243531239</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="BI13" t="n">
         <v>31.37089159565237</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BJ13" t="n">
         <v>30.13097700042267</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="BK13" t="n">
         <v>342</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="BL13" t="n">
         <v>342</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BM13" t="n">
         <v>342</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BN13" t="n">
         <v>342</v>
       </c>
-      <c r="BF13" t="n">
+      <c r="BO13" t="n">
         <v>342</v>
       </c>
-      <c r="BG13" t="n">
+      <c r="BP13" t="n">
         <v>342</v>
       </c>
-      <c r="BH13" t="n">
+      <c r="BQ13" t="n">
         <v>342</v>
       </c>
-      <c r="BI13" t="n">
+      <c r="BR13" t="n">
         <v>342</v>
       </c>
-      <c r="BJ13" t="n">
+      <c r="BS13" t="n">
         <v>342</v>
       </c>
-      <c r="BK13" t="n">
+      <c r="BT13" t="n">
         <v>636</v>
       </c>
-      <c r="BL13" t="n">
+      <c r="BU13" t="n">
         <v>636</v>
       </c>
-      <c r="BM13" t="n">
+      <c r="BV13" t="n">
         <v>636</v>
       </c>
-      <c r="BN13" t="n">
+      <c r="BW13" t="n">
         <v>636</v>
       </c>
-      <c r="BO13" t="n">
+      <c r="BX13" t="n">
         <v>636</v>
       </c>
-      <c r="BP13" t="n">
+      <c r="BY13" t="n">
         <v>636</v>
       </c>
-      <c r="BQ13" t="n">
+      <c r="BZ13" t="n">
         <v>636</v>
       </c>
-      <c r="BR13" t="n">
+      <c r="CA13" t="n">
         <v>636</v>
       </c>
-      <c r="BS13" t="n">
+      <c r="CB13" t="n">
         <v>636</v>
       </c>
-      <c r="BT13" t="n">
+      <c r="CC13" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU13" t="n">
+      <c r="CD13" t="n">
         <v>0.07142857142857142</v>
       </c>
-      <c r="BV13" t="n">
+      <c r="CE13" t="n">
         <v>1</v>
       </c>
-      <c r="BW13" t="n">
+      <c r="CF13" t="n">
         <v>1</v>
       </c>
-      <c r="BX13" t="n">
+      <c r="CG13" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="BY13" t="n">
+      <c r="CH13" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BZ13" t="n">
+      <c r="CI13" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="CA13" t="n">
+      <c r="CJ13" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="CB13" t="n">
+      <c r="CK13" t="n">
         <v>0.02083333333333333</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>498.36</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>21.37</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>498</v>
       </c>
       <c r="C14" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D14" t="n">
         <v>22</v>
-      </c>
-      <c r="D14" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E14" t="n">
         <v>498</v>
@@ -3804,1212 +4255,1377 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>495.4015747682836</v>
-      </c>
-      <c r="J14" t="n">
-        <v>39.1448006689462</v>
-      </c>
-      <c r="K14" t="n">
-        <v>490.2241012898015</v>
-      </c>
-      <c r="L14" t="n">
-        <v>33.95436957714319</v>
-      </c>
-      <c r="M14" t="n">
-        <v>488.8332030908646</v>
-      </c>
-      <c r="N14" t="n">
-        <v>33.23463630957467</v>
-      </c>
-      <c r="O14" t="n">
-        <v>489.7106559102997</v>
-      </c>
-      <c r="P14" t="n">
-        <v>33.47353111366181</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>495.3292546088373</v>
-      </c>
       <c r="R14" t="n">
-        <v>38.63183604515474</v>
+        <v>495.4</v>
       </c>
       <c r="S14" t="n">
-        <v>490.8286301753149</v>
+        <v>39.14</v>
       </c>
       <c r="T14" t="n">
-        <v>37.45526357617238</v>
+        <v>490.22</v>
       </c>
       <c r="U14" t="n">
-        <v>490.44950430806</v>
+        <v>33.95</v>
       </c>
       <c r="V14" t="n">
-        <v>33.98538102882529</v>
+        <v>488.83</v>
       </c>
       <c r="W14" t="n">
-        <v>489.4903270992272</v>
+        <v>33.23</v>
       </c>
       <c r="X14" t="n">
-        <v>33.10121247372687</v>
+        <v>489.71</v>
       </c>
       <c r="Y14" t="n">
-        <v>488.0112547700446</v>
+        <v>33.47</v>
       </c>
       <c r="Z14" t="n">
-        <v>34.27754972589212</v>
+        <v>495.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>38.63</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>490.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>37.46</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>490.45</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>33.99</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>489.49</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>33.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>488.01</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>34.28</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>500.875</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>500.4833333333333</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>501.3875</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>500.63</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>500.1166666666667</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>500.3571428571428</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>500.75625</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>500.4944444444445</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>500.575</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>61.01892636715267</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>56.87486019518837</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>56.49214408880229</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>51.9487545567745</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>56.51300489464547</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>54.79690703322737</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>53.72624438705445</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>52.06347591826114</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>50.88746775975397</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>322</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>322</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>322</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>322</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>322</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>322</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>322</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>322</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>322</v>
       </c>
-      <c r="BK14" t="n">
+      <c r="BT14" t="n">
         <v>639</v>
       </c>
-      <c r="BL14" t="n">
+      <c r="BU14" t="n">
         <v>639</v>
       </c>
-      <c r="BM14" t="n">
+      <c r="BV14" t="n">
         <v>639</v>
       </c>
-      <c r="BN14" t="n">
+      <c r="BW14" t="n">
         <v>639</v>
       </c>
-      <c r="BO14" t="n">
+      <c r="BX14" t="n">
         <v>639</v>
       </c>
-      <c r="BP14" t="n">
+      <c r="BY14" t="n">
         <v>639</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BZ14" t="n">
         <v>639</v>
       </c>
-      <c r="BR14" t="n">
+      <c r="CA14" t="n">
         <v>639</v>
       </c>
-      <c r="BS14" t="n">
+      <c r="CB14" t="n">
         <v>639</v>
       </c>
-      <c r="BT14" t="n">
+      <c r="CC14" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>1</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>1</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.8</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>0.9565217391304348</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.9629629629629629</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>488.01</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>34.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S15_G4_500_19_REL1</t>
+          <t>S14_G4_501_19_REL1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C15" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D15" t="n">
         <v>19</v>
       </c>
-      <c r="D15" t="n">
-        <v>28.16901408450704</v>
-      </c>
       <c r="E15" t="n">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F15" t="n">
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>488.158654965381</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24.07469070080457</v>
-      </c>
-      <c r="K15" t="n">
-        <v>492.1128889419653</v>
-      </c>
-      <c r="L15" t="n">
-        <v>27.22558856528729</v>
-      </c>
-      <c r="M15" t="n">
-        <v>490.8376950538446</v>
-      </c>
-      <c r="N15" t="n">
-        <v>25.51481099192275</v>
-      </c>
-      <c r="O15" t="n">
-        <v>493.2075165501811</v>
-      </c>
-      <c r="P15" t="n">
-        <v>24.28095365097948</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>492.9855745992579</v>
-      </c>
       <c r="R15" t="n">
-        <v>23.29067694519877</v>
+        <v>494.88</v>
       </c>
       <c r="S15" t="n">
-        <v>493.1340738837637</v>
+        <v>18.48</v>
       </c>
       <c r="T15" t="n">
-        <v>23.67512205583291</v>
+        <v>494.44</v>
       </c>
       <c r="U15" t="n">
-        <v>494.0157975799722</v>
+        <v>20.29</v>
       </c>
       <c r="V15" t="n">
-        <v>22.57977024144559</v>
+        <v>500.47</v>
       </c>
       <c r="W15" t="n">
-        <v>496.1452095737212</v>
+        <v>22.73</v>
       </c>
       <c r="X15" t="n">
-        <v>23.41038438890987</v>
+        <v>501.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>495.2190234682591</v>
+        <v>25.77</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.07033005429284</v>
+        <v>501.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>24.39</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>501.46</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>23.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>501.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>23.02</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>499.59</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>22.48</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>499.8</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>21.94</v>
       </c>
       <c r="AJ15" t="n">
-        <v>497.125</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>498.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>498.8375</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>499.1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>498.8916666666667</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>498.9928571428571</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>499.375</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>499.2833333333334</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>499.145</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>53.18467236902001</v>
+        <v>503.725</v>
       </c>
       <c r="AT15" t="n">
-        <v>49.13609218848763</v>
+        <v>501.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>45.77729889093501</v>
+        <v>501.1875</v>
       </c>
       <c r="AV15" t="n">
-        <v>42.39610831196656</v>
+        <v>500.27</v>
       </c>
       <c r="AW15" t="n">
-        <v>40.54191161282633</v>
+        <v>500.2166666666666</v>
       </c>
       <c r="AX15" t="n">
-        <v>39.23637096014932</v>
+        <v>499.9357142857143</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.34279548989336</v>
+        <v>500.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>35.58655723100446</v>
+        <v>500.15</v>
       </c>
       <c r="BA15" t="n">
-        <v>34.22227308347591</v>
+        <v>500.24</v>
       </c>
       <c r="BB15" t="n">
-        <v>357</v>
+        <v>52.58896628571435</v>
       </c>
       <c r="BC15" t="n">
-        <v>357</v>
+        <v>44.96614467203817</v>
       </c>
       <c r="BD15" t="n">
-        <v>357</v>
+        <v>41.17283502201421</v>
       </c>
       <c r="BE15" t="n">
-        <v>357</v>
+        <v>41.05651105488629</v>
       </c>
       <c r="BF15" t="n">
-        <v>357</v>
+        <v>39.5990705558715</v>
       </c>
       <c r="BG15" t="n">
-        <v>357</v>
+        <v>37.22848577448759</v>
       </c>
       <c r="BH15" t="n">
-        <v>357</v>
+        <v>35.9421062265416</v>
       </c>
       <c r="BI15" t="n">
-        <v>357</v>
+        <v>34.77985927388308</v>
       </c>
       <c r="BJ15" t="n">
-        <v>357</v>
+        <v>33.92053065622648</v>
       </c>
       <c r="BK15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BL15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BM15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BN15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BO15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BP15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BQ15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BR15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BS15" t="n">
-        <v>669</v>
+        <v>421</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.9166666666666666</v>
+        <v>669</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.8235294117647058</v>
+        <v>669</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.9565217391304348</v>
+        <v>669</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.9333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.9696969696969697</v>
+        <v>669</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.8809523809523809</v>
+        <v>669</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.8936170212765957</v>
+        <v>669</v>
       </c>
       <c r="CB15" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CE15" t="n">
         <v>0.8421052631578947</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0.6279069767441861</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>499.8</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>21.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S14_G4_501_19_REL1</t>
+          <t>S15_G4_500_19_REL1</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C16" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D16" t="n">
         <v>19</v>
       </c>
-      <c r="D16" t="n">
-        <v>28.16901408450704</v>
-      </c>
       <c r="E16" t="n">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F16" t="n">
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>494.8773879187299</v>
-      </c>
-      <c r="J16" t="n">
-        <v>18.47538132197733</v>
-      </c>
-      <c r="K16" t="n">
-        <v>494.4423500055868</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20.28584147534537</v>
-      </c>
-      <c r="M16" t="n">
-        <v>500.4663739329526</v>
-      </c>
-      <c r="N16" t="n">
-        <v>22.72615853012904</v>
-      </c>
-      <c r="O16" t="n">
-        <v>501.2012466167823</v>
-      </c>
-      <c r="P16" t="n">
-        <v>25.77486365286976</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>501.1981046452511</v>
-      </c>
       <c r="R16" t="n">
-        <v>24.39441128138288</v>
+        <v>488.16</v>
       </c>
       <c r="S16" t="n">
-        <v>501.4576990328269</v>
+        <v>24.07</v>
       </c>
       <c r="T16" t="n">
-        <v>23.72731174816613</v>
+        <v>492.11</v>
       </c>
       <c r="U16" t="n">
-        <v>501.643561121827</v>
+        <v>27.23</v>
       </c>
       <c r="V16" t="n">
-        <v>23.01959413113126</v>
+        <v>490.84</v>
       </c>
       <c r="W16" t="n">
-        <v>499.5924938490389</v>
+        <v>25.51</v>
       </c>
       <c r="X16" t="n">
-        <v>22.47732536318543</v>
+        <v>493.21</v>
       </c>
       <c r="Y16" t="n">
-        <v>499.8022482623585</v>
+        <v>24.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.93566954951315</v>
+        <v>492.99</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>23.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>493.13</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>23.68</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>494.02</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>22.58</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>496.15</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>23.41</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>495.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>24.07</v>
       </c>
       <c r="AJ16" t="n">
-        <v>503.725</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>501.75</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>501.1875</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>500.27</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>500.2166666666666</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>499.9357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>500.3</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>500.15</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>500.24</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>52.58896628571435</v>
+        <v>497.125</v>
       </c>
       <c r="AT16" t="n">
-        <v>44.96614467203817</v>
+        <v>498.3333333333333</v>
       </c>
       <c r="AU16" t="n">
-        <v>41.17283502201421</v>
+        <v>498.8375</v>
       </c>
       <c r="AV16" t="n">
-        <v>41.05651105488629</v>
+        <v>499.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>39.5990705558715</v>
+        <v>498.8916666666667</v>
       </c>
       <c r="AX16" t="n">
-        <v>37.22848577448759</v>
+        <v>498.9928571428571</v>
       </c>
       <c r="AY16" t="n">
-        <v>35.9421062265416</v>
+        <v>499.375</v>
       </c>
       <c r="AZ16" t="n">
-        <v>34.77985927388308</v>
+        <v>499.2833333333334</v>
       </c>
       <c r="BA16" t="n">
-        <v>33.92053065622648</v>
+        <v>499.145</v>
       </c>
       <c r="BB16" t="n">
-        <v>421</v>
+        <v>53.18467236902001</v>
       </c>
       <c r="BC16" t="n">
-        <v>421</v>
+        <v>49.13609218848763</v>
       </c>
       <c r="BD16" t="n">
-        <v>421</v>
+        <v>45.77729889093501</v>
       </c>
       <c r="BE16" t="n">
-        <v>421</v>
+        <v>42.39610831196656</v>
       </c>
       <c r="BF16" t="n">
-        <v>421</v>
+        <v>40.54191161282633</v>
       </c>
       <c r="BG16" t="n">
-        <v>421</v>
+        <v>39.23637096014932</v>
       </c>
       <c r="BH16" t="n">
-        <v>421</v>
+        <v>37.34279548989336</v>
       </c>
       <c r="BI16" t="n">
-        <v>421</v>
+        <v>35.58655723100446</v>
       </c>
       <c r="BJ16" t="n">
-        <v>421</v>
+        <v>34.22227308347591</v>
       </c>
       <c r="BK16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BL16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BM16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BN16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BO16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BP16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BQ16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BR16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BS16" t="n">
-        <v>669</v>
+        <v>357</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.5625</v>
+        <v>669</v>
       </c>
       <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="CK16" t="n">
         <v>0.8421052631578947</v>
       </c>
-      <c r="BW16" t="n">
-        <v>0.7619047619047619</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>0.6153846153846154</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>0.6279069767441861</v>
+      <c r="CL16" t="n">
+        <v>495.22</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>24.07</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S17_G4_500_22_REL1</t>
+          <t>S16_G4_498_19_REL1</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D17" t="n">
-        <v>32.61675315048184</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F17" t="n">
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>77</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>488.5990892631652</v>
-      </c>
-      <c r="J17" t="n">
-        <v>25.50086717008082</v>
-      </c>
-      <c r="K17" t="n">
-        <v>496.276018191478</v>
-      </c>
-      <c r="L17" t="n">
-        <v>27.96664873205365</v>
-      </c>
-      <c r="M17" t="n">
-        <v>498.6097651363598</v>
-      </c>
-      <c r="N17" t="n">
-        <v>28.51587328390523</v>
-      </c>
-      <c r="O17" t="n">
-        <v>499.2823452990999</v>
-      </c>
-      <c r="P17" t="n">
-        <v>26.26624949888522</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>498.9031260424742</v>
-      </c>
       <c r="R17" t="n">
-        <v>24.62116125911504</v>
+        <v>506.85</v>
       </c>
       <c r="S17" t="n">
-        <v>499.5041534142296</v>
+        <v>20.08</v>
       </c>
       <c r="T17" t="n">
-        <v>24.13052652888418</v>
+        <v>502.45</v>
       </c>
       <c r="U17" t="n">
-        <v>500.8299589881772</v>
+        <v>23.3</v>
       </c>
       <c r="V17" t="n">
-        <v>25.59048905758785</v>
+        <v>502.43</v>
       </c>
       <c r="W17" t="n">
-        <v>500.5830496460313</v>
+        <v>21.8</v>
       </c>
       <c r="X17" t="n">
-        <v>24.26219858315963</v>
+        <v>505.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>500.3574981828742</v>
+        <v>25.63</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.14802164145306</v>
+        <v>502.42</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>25.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>500.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>23.98</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>501.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>23.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>501.37</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>502.46</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>501.3</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>501.1833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>500.2375</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>501.68</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>500.8166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>501.2071428571429</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>500.79375</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>500.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>500.845</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>54.55602624825235</v>
+        <v>503.725</v>
       </c>
       <c r="AT17" t="n">
-        <v>47.12872148582952</v>
+        <v>502.25</v>
       </c>
       <c r="AU17" t="n">
-        <v>46.19936248207328</v>
+        <v>502.1375</v>
       </c>
       <c r="AV17" t="n">
-        <v>42.83290324038285</v>
+        <v>501.35</v>
       </c>
       <c r="AW17" t="n">
-        <v>40.71281193378266</v>
+        <v>501.1083333333333</v>
       </c>
       <c r="AX17" t="n">
-        <v>38.53430687222036</v>
+        <v>501.1642857142857</v>
       </c>
       <c r="AY17" t="n">
-        <v>38.2573680607736</v>
+        <v>500.9625</v>
       </c>
       <c r="AZ17" t="n">
-        <v>36.82403728846448</v>
+        <v>501.0388888888889</v>
       </c>
       <c r="BA17" t="n">
-        <v>35.8679658609183</v>
+        <v>500.62</v>
       </c>
       <c r="BB17" t="n">
-        <v>355</v>
+        <v>49.12890569715552</v>
       </c>
       <c r="BC17" t="n">
-        <v>355</v>
+        <v>42.87875348001619</v>
       </c>
       <c r="BD17" t="n">
-        <v>355</v>
+        <v>38.79972414528227</v>
       </c>
       <c r="BE17" t="n">
-        <v>355</v>
+        <v>36.66043507652358</v>
       </c>
       <c r="BF17" t="n">
-        <v>355</v>
+        <v>35.20506493705447</v>
       </c>
       <c r="BG17" t="n">
-        <v>355</v>
+        <v>33.6020005174619</v>
       </c>
       <c r="BH17" t="n">
-        <v>355</v>
+        <v>32.21720958975187</v>
       </c>
       <c r="BI17" t="n">
-        <v>355</v>
+        <v>30.99934836033545</v>
       </c>
       <c r="BJ17" t="n">
-        <v>355</v>
+        <v>30.03507283160805</v>
       </c>
       <c r="BK17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BL17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BM17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BN17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BO17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BP17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BQ17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BR17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BS17" t="n">
-        <v>669</v>
+        <v>365</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BU17" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.05263157894736842</v>
+        <v>669</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.03846153846153846</v>
+        <v>669</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.7777777777777778</v>
+        <v>669</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.6764705882352942</v>
+        <v>669</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.6829268292682927</v>
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0.6176470588235294</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0.5740740740740741</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0.5903614457831325</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0.6626506024096386</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>502.46</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>22.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S16_G4_498_19_REL1</t>
+          <t>S17_G4_500_22_REL1</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C18" t="n">
-        <v>19</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D18" t="n">
-        <v>28.16901408450704</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F18" t="n">
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>506.8467515305121</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20.07799737591575</v>
-      </c>
-      <c r="K18" t="n">
-        <v>502.4542521546014</v>
-      </c>
-      <c r="L18" t="n">
-        <v>23.30173831019669</v>
-      </c>
-      <c r="M18" t="n">
-        <v>502.4323596565945</v>
-      </c>
-      <c r="N18" t="n">
-        <v>21.80490897186552</v>
-      </c>
-      <c r="O18" t="n">
-        <v>505.1960226817174</v>
-      </c>
-      <c r="P18" t="n">
-        <v>25.63076720591933</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>502.4202161849751</v>
-      </c>
       <c r="R18" t="n">
-        <v>25.25509076727671</v>
+        <v>488.6</v>
       </c>
       <c r="S18" t="n">
-        <v>500.698496437555</v>
+        <v>25.5</v>
       </c>
       <c r="T18" t="n">
-        <v>23.97897177491226</v>
+        <v>496.28</v>
       </c>
       <c r="U18" t="n">
-        <v>501.2643595337804</v>
+        <v>27.97</v>
       </c>
       <c r="V18" t="n">
-        <v>23.73219821228431</v>
+        <v>498.61</v>
       </c>
       <c r="W18" t="n">
-        <v>501.3686812090062</v>
+        <v>28.52</v>
       </c>
       <c r="X18" t="n">
-        <v>22.80405780056845</v>
+        <v>499.28</v>
       </c>
       <c r="Y18" t="n">
-        <v>502.4572373887922</v>
+        <v>26.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>22.39774733550942</v>
+        <v>498.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>24.62</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>499.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>24.13</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>500.83</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>25.59</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>500.58</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>24.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>500.36</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>24.15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>503.725</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>502.25</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>502.1375</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>501.35</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>501.1083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>501.1642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>500.9625</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>501.0388888888889</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>500.62</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>49.12890569715552</v>
+        <v>501.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>42.87875348001619</v>
+        <v>501.1833333333333</v>
       </c>
       <c r="AU18" t="n">
-        <v>38.79972414528227</v>
+        <v>500.2375</v>
       </c>
       <c r="AV18" t="n">
-        <v>36.66043507652358</v>
+        <v>501.68</v>
       </c>
       <c r="AW18" t="n">
-        <v>35.20506493705447</v>
+        <v>500.8166666666667</v>
       </c>
       <c r="AX18" t="n">
-        <v>33.6020005174619</v>
+        <v>501.2071428571429</v>
       </c>
       <c r="AY18" t="n">
-        <v>32.21720958975187</v>
+        <v>500.79375</v>
       </c>
       <c r="AZ18" t="n">
-        <v>30.99934836033545</v>
+        <v>500.5833333333333</v>
       </c>
       <c r="BA18" t="n">
-        <v>30.03507283160805</v>
+        <v>500.845</v>
       </c>
       <c r="BB18" t="n">
-        <v>365</v>
+        <v>54.55602624825235</v>
       </c>
       <c r="BC18" t="n">
-        <v>365</v>
+        <v>47.12872148582952</v>
       </c>
       <c r="BD18" t="n">
-        <v>365</v>
+        <v>46.19936248207328</v>
       </c>
       <c r="BE18" t="n">
-        <v>365</v>
+        <v>42.83290324038285</v>
       </c>
       <c r="BF18" t="n">
-        <v>365</v>
+        <v>40.71281193378266</v>
       </c>
       <c r="BG18" t="n">
-        <v>365</v>
+        <v>38.53430687222036</v>
       </c>
       <c r="BH18" t="n">
-        <v>365</v>
+        <v>38.2573680607736</v>
       </c>
       <c r="BI18" t="n">
-        <v>365</v>
+        <v>36.82403728846448</v>
       </c>
       <c r="BJ18" t="n">
-        <v>365</v>
+        <v>35.8679658609183</v>
       </c>
       <c r="BK18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BL18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BM18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BN18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BO18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BP18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BQ18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BR18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BS18" t="n">
-        <v>669</v>
+        <v>355</v>
       </c>
       <c r="BT18" t="n">
-        <v>0.6428571428571429</v>
+        <v>669</v>
       </c>
       <c r="BU18" t="n">
-        <v>0.7083333333333334</v>
+        <v>669</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.6176470588235294</v>
+        <v>669</v>
       </c>
       <c r="BW18" t="n">
-        <v>0.5454545454545454</v>
+        <v>669</v>
       </c>
       <c r="BX18" t="n">
-        <v>0.5740740740740741</v>
+        <v>669</v>
       </c>
       <c r="BY18" t="n">
-        <v>0.59375</v>
+        <v>669</v>
       </c>
       <c r="BZ18" t="n">
-        <v>0.6216216216216216</v>
+        <v>669</v>
       </c>
       <c r="CA18" t="n">
-        <v>0.5903614457831325</v>
+        <v>669</v>
       </c>
       <c r="CB18" t="n">
-        <v>0.6626506024096386</v>
+        <v>669</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>0.6829268292682927</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>500.36</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>24.15</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>499</v>
       </c>
       <c r="C19" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D19" t="n">
         <v>19</v>
-      </c>
-      <c r="D19" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E19" t="n">
         <v>499</v>
@@ -5034,228 +5650,261 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>505.9207822568125</v>
-      </c>
-      <c r="J19" t="n">
-        <v>17.80787817425256</v>
-      </c>
-      <c r="K19" t="n">
-        <v>501.2895413654738</v>
-      </c>
-      <c r="L19" t="n">
-        <v>19.82360589805057</v>
-      </c>
-      <c r="M19" t="n">
-        <v>503.8307232512527</v>
-      </c>
-      <c r="N19" t="n">
-        <v>21.90448365620571</v>
-      </c>
-      <c r="O19" t="n">
-        <v>504.4112077575541</v>
-      </c>
-      <c r="P19" t="n">
-        <v>25.14864384943601</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>507.9152831284208</v>
-      </c>
       <c r="R19" t="n">
-        <v>27.32512229725995</v>
+        <v>505.92</v>
       </c>
       <c r="S19" t="n">
-        <v>506.9288274892439</v>
+        <v>17.81</v>
       </c>
       <c r="T19" t="n">
-        <v>25.55048517602608</v>
+        <v>501.29</v>
       </c>
       <c r="U19" t="n">
-        <v>505.4180740543305</v>
+        <v>19.82</v>
       </c>
       <c r="V19" t="n">
-        <v>23.54746666041668</v>
+        <v>503.83</v>
       </c>
       <c r="W19" t="n">
-        <v>505.8185992891666</v>
+        <v>21.9</v>
       </c>
       <c r="X19" t="n">
-        <v>24.2249406537346</v>
+        <v>504.41</v>
       </c>
       <c r="Y19" t="n">
-        <v>503.9645277180852</v>
+        <v>25.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.91330985415931</v>
+        <v>507.92</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>27.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>506.93</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>25.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>505.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>23.55</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>505.82</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>24.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>503.96</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>23.91</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>501.5</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>500.45</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>500.325</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>500.43</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>500.35</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>500.1857142857143</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>500.21875</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>500.45</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>500.405</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>49.82368914482347</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>43.1101012911514</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>39.11833809097723</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>36.38495705645398</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>35.56652218027509</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>35.6784420132073</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>35.02760908822496</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>34.40869964283904</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>33.2573446775295</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>397</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>397</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>397</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>397</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>397</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>397</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>397</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>397</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>397</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.5</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.5294117647058824</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.5227272727272727</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.6415094339622641</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.6825396825396826</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.6438356164383562</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.6891891891891891</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>503.96</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>23.91</v>
       </c>
     </row>
     <row r="20">
@@ -5268,10 +5917,10 @@
         <v>500</v>
       </c>
       <c r="C20" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D20" t="n">
         <v>21</v>
-      </c>
-      <c r="D20" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E20" t="n">
         <v>500</v>
@@ -5280,228 +5929,261 @@
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>81.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>496.3557212104486</v>
-      </c>
-      <c r="J20" t="n">
-        <v>20.53016832865541</v>
-      </c>
-      <c r="K20" t="n">
-        <v>498.4861371843885</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19.16169884220198</v>
-      </c>
-      <c r="M20" t="n">
-        <v>502.7278478350046</v>
-      </c>
-      <c r="N20" t="n">
-        <v>19.96708439598583</v>
-      </c>
-      <c r="O20" t="n">
-        <v>501.4471425910064</v>
-      </c>
-      <c r="P20" t="n">
-        <v>16.82295064445798</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>501.4057434999642</v>
-      </c>
       <c r="R20" t="n">
-        <v>17.5693294936334</v>
+        <v>496.36</v>
       </c>
       <c r="S20" t="n">
-        <v>502.0890965945078</v>
+        <v>20.53</v>
       </c>
       <c r="T20" t="n">
-        <v>18.89249289190594</v>
+        <v>498.49</v>
       </c>
       <c r="U20" t="n">
-        <v>502.2812469155676</v>
+        <v>19.16</v>
       </c>
       <c r="V20" t="n">
-        <v>18.70983488698894</v>
+        <v>502.73</v>
       </c>
       <c r="W20" t="n">
-        <v>503.5584254400276</v>
+        <v>19.97</v>
       </c>
       <c r="X20" t="n">
-        <v>18.96701917940287</v>
+        <v>501.45</v>
       </c>
       <c r="Y20" t="n">
-        <v>503.5984274048271</v>
+        <v>16.82</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.30565709296362</v>
+        <v>501.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>17.57</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>502.09</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>18.89</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>502.28</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>18.71</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>503.56</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>18.97</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>503.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>19.31</v>
       </c>
       <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
         <v>508.2</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AT20" t="n">
         <v>505.8</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AU20" t="n">
         <v>504.15</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AV20" t="n">
         <v>503.35</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AW20" t="n">
         <v>502.3416666666666</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AX20" t="n">
         <v>501.5928571428572</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AY20" t="n">
         <v>500.9375</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AZ20" t="n">
         <v>500.6777777777778</v>
       </c>
-      <c r="AR20" t="n">
+      <c r="BA20" t="n">
         <v>501.015</v>
       </c>
-      <c r="AS20" t="n">
+      <c r="BB20" t="n">
         <v>49.76052652454553</v>
       </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>42.48050533283866</v>
       </c>
-      <c r="AU20" t="n">
+      <c r="BD20" t="n">
         <v>38.40152991743949</v>
       </c>
-      <c r="AV20" t="n">
+      <c r="BE20" t="n">
         <v>35.43765652522751</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="BF20" t="n">
         <v>33.00795253504155</v>
       </c>
-      <c r="AX20" t="n">
+      <c r="BG20" t="n">
         <v>32.18138246798948</v>
       </c>
-      <c r="AY20" t="n">
+      <c r="BH20" t="n">
         <v>33.21985240409716</v>
       </c>
-      <c r="AZ20" t="n">
+      <c r="BI20" t="n">
         <v>32.76798158696917</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BJ20" t="n">
         <v>32.21063139710242</v>
       </c>
-      <c r="BB20" t="n">
+      <c r="BK20" t="n">
         <v>414</v>
       </c>
-      <c r="BC20" t="n">
+      <c r="BL20" t="n">
         <v>414</v>
       </c>
-      <c r="BD20" t="n">
+      <c r="BM20" t="n">
         <v>414</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BN20" t="n">
         <v>414</v>
       </c>
-      <c r="BF20" t="n">
+      <c r="BO20" t="n">
         <v>414</v>
       </c>
-      <c r="BG20" t="n">
+      <c r="BP20" t="n">
         <v>414</v>
       </c>
-      <c r="BH20" t="n">
+      <c r="BQ20" t="n">
         <v>414</v>
       </c>
-      <c r="BI20" t="n">
+      <c r="BR20" t="n">
         <v>414</v>
       </c>
-      <c r="BJ20" t="n">
+      <c r="BS20" t="n">
         <v>414</v>
       </c>
-      <c r="BK20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR20" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS20" t="n">
-        <v>669</v>
-      </c>
       <c r="BT20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC20" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="BU20" t="n">
+      <c r="CD20" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BV20" t="n">
+      <c r="CE20" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BW20" t="n">
+      <c r="CF20" t="n">
         <v>0.5813953488372093</v>
       </c>
-      <c r="BX20" t="n">
+      <c r="CG20" t="n">
         <v>0.6511627906976745</v>
       </c>
-      <c r="BY20" t="n">
+      <c r="CH20" t="n">
         <v>0.7674418604651163</v>
       </c>
-      <c r="BZ20" t="n">
+      <c r="CI20" t="n">
         <v>0.7674418604651163</v>
       </c>
-      <c r="CA20" t="n">
+      <c r="CJ20" t="n">
         <v>0.7674418604651163</v>
       </c>
-      <c r="CB20" t="n">
+      <c r="CK20" t="n">
         <v>0.7906976744186046</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>503.6</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>19.31</v>
       </c>
     </row>
     <row r="21">
@@ -5514,10 +6196,10 @@
         <v>501</v>
       </c>
       <c r="C21" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D21" t="n">
         <v>19</v>
-      </c>
-      <c r="D21" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E21" t="n">
         <v>501</v>
@@ -5526,228 +6208,261 @@
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>495.7978840010492</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11.81925126164625</v>
-      </c>
-      <c r="K21" t="n">
-        <v>495.2058630694556</v>
-      </c>
-      <c r="L21" t="n">
-        <v>14.86855502829899</v>
-      </c>
-      <c r="M21" t="n">
-        <v>495.4452010221597</v>
-      </c>
-      <c r="N21" t="n">
-        <v>19.27185678409714</v>
-      </c>
-      <c r="O21" t="n">
-        <v>497.8064508289984</v>
-      </c>
-      <c r="P21" t="n">
-        <v>19.6396877212434</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>497.8506258252718</v>
-      </c>
       <c r="R21" t="n">
-        <v>20.19689253911087</v>
+        <v>495.8</v>
       </c>
       <c r="S21" t="n">
-        <v>497.0892855140645</v>
+        <v>11.82</v>
       </c>
       <c r="T21" t="n">
-        <v>20.6068981005626</v>
+        <v>495.21</v>
       </c>
       <c r="U21" t="n">
-        <v>499.4642298190366</v>
+        <v>14.87</v>
       </c>
       <c r="V21" t="n">
-        <v>19.56648726591332</v>
+        <v>495.45</v>
       </c>
       <c r="W21" t="n">
-        <v>500.7876462071751</v>
+        <v>19.27</v>
       </c>
       <c r="X21" t="n">
-        <v>18.85504362212557</v>
+        <v>497.81</v>
       </c>
       <c r="Y21" t="n">
-        <v>501.3678988963466</v>
+        <v>19.64</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.06096107653233</v>
+        <v>497.85</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>497.09</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>20.61</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>499.46</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>19.57</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>500.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>18.86</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>501.37</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>18.06</v>
       </c>
       <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
         <v>495.425</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AT21" t="n">
         <v>497.35</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AU21" t="n">
         <v>498.025</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AV21" t="n">
         <v>498.1</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AW21" t="n">
         <v>499.0083333333333</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AX21" t="n">
         <v>499.4785714285715</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AY21" t="n">
         <v>498.875</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
         <v>499.2444444444445</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="BA21" t="n">
         <v>499.595</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="BB21" t="n">
         <v>50.33829928593138</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="BC21" t="n">
         <v>41.85802392214266</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="BD21" t="n">
         <v>38.46036108774851</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="BE21" t="n">
         <v>38.36052658658377</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="BF21" t="n">
         <v>36.7138701840175</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="BG21" t="n">
         <v>34.93922639121145</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BH21" t="n">
         <v>33.46616761746107</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="BI21" t="n">
         <v>32.33739187968391</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BJ21" t="n">
         <v>31.21635749090531</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BK21" t="n">
         <v>316</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BL21" t="n">
         <v>316</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BM21" t="n">
         <v>316</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BN21" t="n">
         <v>316</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BO21" t="n">
         <v>316</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BP21" t="n">
         <v>316</v>
       </c>
-      <c r="BH21" t="n">
+      <c r="BQ21" t="n">
         <v>316</v>
       </c>
-      <c r="BI21" t="n">
+      <c r="BR21" t="n">
         <v>316</v>
       </c>
-      <c r="BJ21" t="n">
+      <c r="BS21" t="n">
         <v>316</v>
       </c>
-      <c r="BK21" t="n">
+      <c r="BT21" t="n">
         <v>592</v>
       </c>
-      <c r="BL21" t="n">
+      <c r="BU21" t="n">
         <v>592</v>
       </c>
-      <c r="BM21" t="n">
+      <c r="BV21" t="n">
         <v>592</v>
       </c>
-      <c r="BN21" t="n">
+      <c r="BW21" t="n">
         <v>592</v>
       </c>
-      <c r="BO21" t="n">
+      <c r="BX21" t="n">
         <v>592</v>
       </c>
-      <c r="BP21" t="n">
+      <c r="BY21" t="n">
         <v>592</v>
       </c>
-      <c r="BQ21" t="n">
+      <c r="BZ21" t="n">
         <v>592</v>
       </c>
-      <c r="BR21" t="n">
+      <c r="CA21" t="n">
         <v>592</v>
       </c>
-      <c r="BS21" t="n">
+      <c r="CB21" t="n">
         <v>592</v>
       </c>
-      <c r="BT21" t="n">
+      <c r="CC21" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="BU21" t="n">
+      <c r="CD21" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="BV21" t="n">
+      <c r="CE21" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BW21" t="n">
+      <c r="CF21" t="n">
         <v>0.5769230769230769</v>
       </c>
-      <c r="BX21" t="n">
+      <c r="CG21" t="n">
         <v>0.6785714285714286</v>
       </c>
-      <c r="BY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ21" t="n">
+      <c r="CH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI21" t="n">
         <v>0.7428571428571429</v>
       </c>
-      <c r="CA21" t="n">
+      <c r="CJ21" t="n">
         <v>0.9428571428571428</v>
       </c>
-      <c r="CB21" t="n">
+      <c r="CK21" t="n">
         <v>0.9459459459459459</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>18.06</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>499.4</v>
       </c>
       <c r="C22" t="n">
+        <v>29.50333580429948</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.9</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.50333580429948</v>
       </c>
       <c r="E22" t="n">
         <v>499.4</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>78.5</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.106</v>
+      </c>
       <c r="I22" t="n">
-        <v>497.9091777846787</v>
+        <v>2.098999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>20.08081150820687</v>
+        <v>2.069</v>
       </c>
       <c r="K22" t="n">
-        <v>497.7325307575251</v>
+        <v>2.0565</v>
       </c>
       <c r="L22" t="n">
-        <v>20.9566271872063</v>
+        <v>2.0635</v>
       </c>
       <c r="M22" t="n">
-        <v>498.2087244460639</v>
+        <v>2.0615</v>
       </c>
       <c r="N22" t="n">
-        <v>21.63713298654529</v>
+        <v>2.341</v>
       </c>
       <c r="O22" t="n">
-        <v>498.2227303117373</v>
+        <v>2.158</v>
       </c>
       <c r="P22" t="n">
-        <v>22.64035653587781</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>498.659063915948</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>22.67225322930481</v>
+        <v>497.9095</v>
       </c>
       <c r="S22" t="n">
-        <v>498.0034928551587</v>
+        <v>20.081</v>
       </c>
       <c r="T22" t="n">
-        <v>22.62246029174877</v>
+        <v>497.7325</v>
       </c>
       <c r="U22" t="n">
-        <v>497.9085193211386</v>
+        <v>20.9565</v>
       </c>
       <c r="V22" t="n">
-        <v>22.57852379184397</v>
+        <v>498.209</v>
       </c>
       <c r="W22" t="n">
-        <v>498.020693759103</v>
+        <v>21.636</v>
       </c>
       <c r="X22" t="n">
-        <v>22.54293120991106</v>
+        <v>498.2230000000001</v>
       </c>
       <c r="Y22" t="n">
-        <v>498.2097241176434</v>
+        <v>22.6395</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.58223971556881</v>
+        <v>498.659</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>22.6725</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>498.003</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>22.6225</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>497.9075</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>22.579</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>498.021</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>22.5425</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>498.2105</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>22.5825</v>
       </c>
       <c r="AJ22" t="n">
-        <v>500.2162500000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>500.0741666666667</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>500.088125</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>500.2165</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>500.073</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>500.088</v>
+      </c>
+      <c r="AV22" t="n">
         <v>500.0600000000001</v>
       </c>
-      <c r="AN22" t="n">
-        <v>499.8820833333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>499.9332142857143</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>499.78625</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>499.75</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.80725</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>51.33646133352579</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>44.71033099959733</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>41.40661744199772</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>39.25627850955128</v>
-      </c>
       <c r="AW22" t="n">
-        <v>37.83209012985996</v>
+        <v>499.8820000000001</v>
       </c>
       <c r="AX22" t="n">
-        <v>36.41888604979921</v>
+        <v>499.933</v>
       </c>
       <c r="AY22" t="n">
-        <v>35.49996856843605</v>
+        <v>499.7865</v>
       </c>
       <c r="AZ22" t="n">
-        <v>34.56533765124017</v>
+        <v>499.7495000000001</v>
       </c>
       <c r="BA22" t="n">
-        <v>33.68424133923943</v>
+        <v>499.8055000000001</v>
       </c>
       <c r="BB22" t="n">
+        <v>51.3365</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>44.711</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>41.406</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>39.256</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>37.83250000000001</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>36.419</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>35.5015</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>34.565</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>33.685</v>
+      </c>
+      <c r="BK22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>354.8</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>646.4</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6824178599178599</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.6530967221184614</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7365747275753496</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.6705444496348304</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7094868951133131</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.7026139918057022</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.7960985794617923</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.7874947025845749</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.7635094748554316</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>498.2105</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.5825</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.313893370663572</v>
       </c>
       <c r="C23" t="n">
+        <v>2.091159433572843</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.410487037944882</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.091159433572843</v>
       </c>
       <c r="E23" t="n">
         <v>1.313893370663572</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03441236008058426</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.468977445995038</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2597042852736044</v>
+      </c>
       <c r="I23" t="n">
-        <v>8.754973081710649</v>
+        <v>0.284121916011234</v>
       </c>
       <c r="J23" t="n">
-        <v>9.055713945968009</v>
+        <v>0.2904062490265735</v>
       </c>
       <c r="K23" t="n">
-        <v>5.934630608465073</v>
+        <v>0.2934957186094974</v>
       </c>
       <c r="L23" t="n">
-        <v>6.560437272837742</v>
+        <v>0.2612374398894615</v>
       </c>
       <c r="M23" t="n">
-        <v>4.866391112317475</v>
+        <v>0.2355346661265989</v>
       </c>
       <c r="N23" t="n">
-        <v>5.352933404540009</v>
+        <v>0.1812500453720451</v>
       </c>
       <c r="O23" t="n">
-        <v>4.585313831895884</v>
+        <v>0.1819080160844747</v>
       </c>
       <c r="P23" t="n">
-        <v>4.703159125347972</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.800795400147204</v>
-      </c>
+        <v>0.2206211327378371</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>5.484379581991842</v>
+        <v>8.753827719166173</v>
       </c>
       <c r="S23" t="n">
-        <v>4.6026025053997</v>
+        <v>9.056595677359009</v>
       </c>
       <c r="T23" t="n">
-        <v>5.028264479520169</v>
+        <v>5.935328550299466</v>
       </c>
       <c r="U23" t="n">
-        <v>4.472025432002492</v>
+        <v>6.560330764286364</v>
       </c>
       <c r="V23" t="n">
-        <v>3.893110538689615</v>
+        <v>4.865626913683161</v>
       </c>
       <c r="W23" t="n">
-        <v>4.34791202278042</v>
+        <v>5.3521519528425</v>
       </c>
       <c r="X23" t="n">
-        <v>3.589498105730828</v>
+        <v>4.585810035774547</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.220880584827525</v>
+        <v>4.703310676086523</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.508474872580338</v>
+        <v>4.801358250811079</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>5.484533156738906</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>4.603407319298218</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.029171612230305</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.472519453636607</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>3.892984107745355</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>4.347651392600253</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.588705784893256</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>4.221065561405582</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.508169225648825</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.603719524032736</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.573944313205978</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.085363605017498</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.604152977359662</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.574308491717008</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.08576781268219</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1.655736439743578</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.332909129339281</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.137426653954293</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.063642187931343</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.033990233256188</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.011999681454084</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>3.97853040858202</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.401080969795071</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>5.027538552240394</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>4.357402362410312</v>
-      </c>
       <c r="AW23" t="n">
-        <v>5.532359763277885</v>
+        <v>1.333971513938738</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.622070939394966</v>
+        <v>1.137356584365695</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.532430664897517</v>
+        <v>1.063847411892085</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.184076907129302</v>
+        <v>1.034191649754079</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.993052715615884</v>
+        <v>1.012430504437613</v>
       </c>
       <c r="BB23" t="n">
+        <v>3.979156582149434</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.401063149070377</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.027713093183464</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.357956305184201</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>5.531843582482483</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>5.623204649158323</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>5.533340358799175</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>5.184114906946127</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>4.993169545014785</v>
+      </c>
+      <c r="BK23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>30.66388240602495</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>29.80003532318641</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.1982784546876297</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.2554931487569358</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.1626335639564578</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.2375518096777992</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2018173167506229</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.2625809835171328</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1211035163701787</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.127159888415032</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.2127762955116497</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>4.221065561405582</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.508169225648825</v>
       </c>
     </row>
   </sheetData>
